--- a/important_mails_2026-10-13.xlsx
+++ b/important_mails_2026-10-13.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -550,21 +550,122 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 17:44:30 +0000</t>
+          <t>Tue, 13 Oct 2026 09:09:18 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Your FBA request is complete (Xqa6kjy120)</t>
+          <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
+ Dzień dobry Weihai EU,
+ Niektóre z Twoich ofert zostały zdezaktywowane w naszych sklepach w Unii Europejskiej (UE) z powodu braku informacji o zgodności z wymogami. Działania te nie mają wpływu na kondycję Twojego konta.
+ Przykłady zdezaktywowanych ofert znajdziesz na dole tej wiadomości e-mail. Aby wyświetlić ich pełną listę, przejdź na stronę „Kondycja konta”. Aby spełnić wymogi rozporządzenia w sprawie ogólnego bezpieczeństwa produktów, zapoznaj się z poniższymi ofertami i dalszymi działaniami do wykonania.
+ Prześlij informacje dotyczące zgodności z wymogami
+ Prześlij informacje dotyczące zgodności z wymogami
+ Jak mogę ponownie aktywować oferty produktów?
+ Aby ponownie aktywować oferty, dostarcz obowiązkowe informacje dotyczące zgodności z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów, postępując zgodnie z poniższymi instrukcjami:
+-
+ Przejdź na stronę Kondycja konta .
+- Wybierz „Dodaj filtry” i w kolumnie „Filtruj według podjętego działania” zaznacz pole „Usunięto ofertę”.
+- Obok zdezaktywowanej oferty produktu kliknij „Prześlij” i postępuj zg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 04:11:35 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
+ Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
+ Skicka in information om överensstämmelse
+ Skicka in information om överensstämmelse
+ Hur återaktiverar jag mina produktposter?
+ Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
+-
+ Gå till sidan Kontostatus .
+- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
+- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
+- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 17:44:30 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (Xqa6kjy120)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -584,39 +685,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:11:27 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -632,39 +733,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 09:31:41 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -680,39 +781,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 04:46:33 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -728,39 +829,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 14:54:13 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ca" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -781,39 +882,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 04:49:48 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -829,39 +930,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 00:57:30 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -879,39 +980,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 05:03:27 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -927,39 +1028,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 16:07:57 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
@@ -973,39 +1074,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:17:16 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1021,87 +1122,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>KYC审核类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:15:33 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -1122,39 +1175,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 20:13:21 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Descargar el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Ya puedes descargar tu declaración fiscal trimestral, que incluye datos como información de identidad, número de transacciones, ingresos y tarifas por servicios y comisiones.
@@ -1170,39 +1223,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:55:18 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1218,39 +1271,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:51:43 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1266,39 +1319,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 13:43:05 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1318,39 +1371,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:48:14 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1374,39 +1427,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 14:20:27 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1430,39 +1483,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:12:07 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -1491,39 +1544,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 17:16:17 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1541,39 +1594,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:57:55 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -1593,39 +1646,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 01:16:04 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1643,39 +1696,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 17:11:11 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1693,39 +1746,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 16:03:12 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1743,39 +1796,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 07:35:36 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -1802,39 +1855,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 13:20:34 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1852,39 +1905,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:56:57 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1900,39 +1953,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1950,39 +2003,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 13:15:21 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2000,39 +2053,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 11:16:06 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2050,39 +2103,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 10:16:15 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2100,39 +2153,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 13:03:41 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -2145,56 +2198,6 @@
 Affected Product(s):
 B0FD8VC559
  SPC-EUAmazon-1600890627600107</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 6 Oct 2026 10:13:01 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
         </is>
       </c>
     </row>
@@ -5743,21 +5746,69 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Sat, 3 Oct 2026 17:10:17 +0000</t>
+          <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
+          <t>FBA reimbursement notification</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 3 Oct 2026 17:10:17 +0000</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5778,39 +5829,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 04:56:42 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5826,39 +5877,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5874,39 +5925,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Jl40SY3EId)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5926,39 +5977,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5978,39 +6029,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6026,39 +6077,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6074,39 +6125,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6122,39 +6173,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6179,39 +6230,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6227,39 +6278,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -6280,39 +6331,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6328,39 +6379,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6376,39 +6427,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6428,39 +6479,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6476,39 +6527,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6524,39 +6575,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -6572,39 +6623,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6620,39 +6671,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -6675,39 +6726,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6723,39 +6774,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 05:13:12 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6771,39 +6822,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 04:57:09 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6819,39 +6870,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:03:28 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6867,39 +6918,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6915,39 +6966,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6963,39 +7014,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 05:13:35 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Pista ferroviaria elettrica a cubi da 145 pezzi, set trenino 3D antigravità, gioco fai da te per costruire percorsi, giocattolo educativo STEM e idea regalo creativa per bambini da 3 a 8 anni
@@ -7016,39 +7067,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7068,39 +7119,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7120,39 +7171,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -7168,39 +7219,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7220,39 +7271,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7272,39 +7323,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7324,39 +7375,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 12:37:44 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7373,39 +7424,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 17:07:48 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Ver el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Presentamos tu declaración fiscal trimestral a la autoridad tributaria china. Ya puedes descargar la declaración para consultarla.
@@ -7421,39 +7472,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 13:27:57 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Last chance to register for Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-11/7z5qvbd/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qvbh/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
@@ -7468,39 +7519,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:07:50 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7520,39 +7571,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 12:34:14 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Registration closes this Friday—save $200 with your exclusive code</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-15/7z5szk3/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5szk6/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
@@ -7566,39 +7617,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Strategies built for sellers at your stage—plus $200 off</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
 [Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
@@ -7612,39 +7663,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7664,39 +7715,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7713,39 +7764,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -7765,39 +7816,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>The Accelerate 2026 agenda got even better. See what's new.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
@@ -7815,39 +7866,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 5 Oct 2026 22:52:24 +0000</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 6 Oct 2026 10:13:01 +0000</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7865,39 +7916,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 5 Oct 2026 14:42:52 +0000</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 5 Oct 2026 22:52:24 +0000</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7915,39 +7966,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 3 Oct 2026 22:29:49 +0000</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 5 Oct 2026 14:42:52 +0000</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7965,39 +8016,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 3 Oct 2026 22:29:49 +0000</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8015,39 +8066,89 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8065,39 +8166,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8115,39 +8216,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -8175,39 +8276,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -8226,39 +8327,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -8277,39 +8378,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8327,39 +8428,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -8377,39 +8478,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:57:06 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Dokończenie rejestracji w ramach ROP i uzyskanie częściowego zwrotu kosztów w Polsce
@@ -8426,39 +8527,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -8476,39 +8577,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:28:03 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Få ersättning för kostnader för överensstämmelse med EPR-förpackningar</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför EPR-registreringen och få en del av kostnaderna återbetalda i Sverige
@@ -8526,39 +8627,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:29 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8577,39 +8678,39 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:17 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8628,39 +8729,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 07:40:02 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>"pli-cn-seller-compliance@amazon.com" &lt;pli-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]
@@ -8690,39 +8791,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:44:09 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>cscompliance-docreview-seller@amazon.de</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>Problem gelöst (Anfrage Nr.: 13280404852)</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>96
 Problem gelöst (Anfrage Nr.: 13280404852)
@@ -8744,41 +8845,41 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:42:38 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY,
  MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document
  Review</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8796,40 +8897,40 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 08:56:32 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -8854,39 +8955,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -8913,40 +9014,40 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Submit proof of insurance by January 18 to avoid listing
  deactivation</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
@@ -8962,40 +9063,40 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -9014,39 +9115,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 18:31:30 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -9062,39 +9163,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 17:35:22 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -9108,40 +9209,40 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 16:48:26 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -9157,39 +9258,39 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 13:33:18 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -9205,39 +9306,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 11:35:34 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Prime 会员大促明天开始 — 提交价格折扣和优惠券的最后时刻</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -9268,39 +9369,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 09:36:33 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -9316,39 +9417,39 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 17:30:23 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -9362,40 +9463,40 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 16:55:10 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -9411,39 +9512,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 13:28:44 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -9459,39 +9560,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 09:30:30 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -9507,39 +9608,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 03:30:58 +0000</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -9555,40 +9656,40 @@
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 01:04:45 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -9604,39 +9705,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 17:20:44 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -9650,40 +9751,40 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -9699,39 +9800,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 19:32:16 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -9747,39 +9848,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 19:31:54 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -9795,39 +9896,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 18:59:51 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -9843,40 +9944,40 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 18:22:14 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -9892,39 +9993,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 17:14:32 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -9938,40 +10039,40 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 16:48:36 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -9987,39 +10088,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 16:38:58 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>Austrian Parcel Tax now in effect</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -10037,39 +10138,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 08:41:07 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E190" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>Zmiana kategorii opłat obowiązująca od 31 października 2026 r.</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Zmiana kategorii opłat w przypadku niektórych Twoich produktów w europejskich sklepach Amazon
@@ -10083,39 +10184,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 07:57:37 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F191" s="2" t="inlineStr">
         <is>
           <t>Actualización de las categorías de tarifas con entrada en vigor el 31 de octubre de 2026</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>96
  Se asignarán algunos de tus ASIN a otra categoría de tarifa en nuestras tiendas europeas.
@@ -10129,39 +10230,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 07:49:32 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F192" s="2" t="inlineStr">
         <is>
           <t>Categorie di commissioni aggiornate dal 31 ottobre 2026</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>96
  Alcuni dei tuoi ASIN verranno assegnati a una categoria di commissioni diversa nei nostri negozi europei
@@ -10174,39 +10275,39 @@
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 07:46:36 +0000</t>
         </is>
       </c>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr">
         <is>
           <t>Update van kostencategorieën, met ingang van 31 oktober 2026</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>96
  Enkele van je ASIN-codes worden toegewezen aan een andere kostencategorie in onze Europese winkels
@@ -10219,39 +10320,39 @@
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 02:30:17 +0000</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 09/2026</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -10269,39 +10370,39 @@
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 08:58:18 +0000</t>
         </is>
       </c>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk
  96
@@ -10311,39 +10412,39 @@
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:54:05 +0000</t>
         </is>
       </c>
-      <c r="E194" s="2" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="F196" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Mzyxxel 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -10367,39 +10468,39 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:17 +0000</t>
         </is>
       </c>
-      <c r="E195" s="2" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="F197" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -10415,40 +10516,40 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:41 +0000</t>
         </is>
       </c>
-      <c r="E196" s="2" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -10464,39 +10565,39 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:40 +0000</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="F199" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -10510,40 +10611,40 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:39 +0000</t>
         </is>
       </c>
-      <c r="E198" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -10559,39 +10660,39 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:28 +0000</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -10607,39 +10708,39 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:08:10 +0000</t>
         </is>
       </c>
-      <c r="E200" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -10655,39 +10756,39 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:44:41 +0000</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -10703,39 +10804,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 05:15:49 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -10756,39 +10857,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:31:24 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026
  96
@@ -10798,39 +10899,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 09:39:36 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Seller News: September 2026
  96
@@ -10840,39 +10941,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 05:03:27 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>Manage returns with rules, not one-offs</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Automate return decisions so you're not handling each one manually.
@@ -10894,39 +10995,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 00:32:28 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>亚马逊卖家平台通知 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F208" s="2" t="inlineStr">
         <is>
           <t>解决定价错误以重新启售停售商品</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>96
  因错价而被禁止显示
@@ -10964,39 +11065,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 14:10:37 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F209" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -11011,39 +11112,39 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:51:02 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F210" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>96
  Actualización de estado de mercancías peligrosas
@@ -11063,39 +11164,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:45:44 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>96
  Status materiałów niebezpiecznych (hazmat)
@@ -11115,39 +11216,39 @@
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:03:52 +0000</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F212" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr"/>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Aggiornamento dello stato delle merci pericolose
@@ -11168,40 +11269,40 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:20:24 +0000</t>
         </is>
       </c>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="F213" s="2" t="inlineStr">
         <is>
           <t>Soluciona los errores de precio para restablecer los listings
  desactivados.</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr"/>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>96
  Eliminar errores de precio
@@ -11222,39 +11323,39 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 13:01:08 +0000</t>
         </is>
       </c>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="E214" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="F214" s="2" t="inlineStr">
         <is>
           <t>【最后机会】9月23日前提交Prime 会员大促活动</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -11286,39 +11387,39 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 15:02:02 +0000</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F215" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13291403212&lt;/p&gt;
@@ -11333,39 +11434,39 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 16:29:22 +0000</t>
         </is>
       </c>
-      <c r="E214" s="2" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>Support Vendeur Amazon &lt;merch.service05@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="F216" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13289094602&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>96
 &lt;p&gt;Merci d'avoir créé un nouveau Cas: -- 13289094602&lt;/p&gt;
@@ -11380,39 +11481,39 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:36:30 +0000</t>
         </is>
       </c>
-      <c r="E215" s="2" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -11435,39 +11536,39 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:32:49 +0000</t>
         </is>
       </c>
-      <c r="E216" s="2" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Status materiałów niebezpiecznych (hazmat)
@@ -11490,39 +11591,39 @@
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr">
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:02:50 +0000</t>
         </is>
       </c>
-      <c r="E217" s="2" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F219" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -11545,39 +11646,39 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F220" s="2" t="inlineStr">
         <is>
           <t>Recover between 60-80%* from returns</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>96
  We handle the grading and reselling. You keep control of pricing and recover value.
@@ -11600,39 +11701,39 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:54:49 +0000</t>
         </is>
       </c>
-      <c r="E219" s="2" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders
  96
@@ -11643,39 +11744,39 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 20:33:01 +0000</t>
         </is>
       </c>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -11691,39 +11792,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 03:07:33 +0000</t>
         </is>
       </c>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-15</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11747,39 +11848,39 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
         </is>
       </c>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -11802,39 +11903,39 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
         </is>
       </c>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="E225" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="F225" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-08</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11858,39 +11959,39 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 17:17:49 +0000</t>
         </is>
       </c>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded, and unfulfillable inventory by 22nd Oct 2026</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -11905,39 +12006,39 @@
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:29:10 +0000</t>
         </is>
       </c>
-      <c r="E225" s="2" t="inlineStr">
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-01</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -11958,39 +12059,39 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 03:52:36 +0000</t>
         </is>
       </c>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="F228" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12014,39 +12115,39 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:54:38 +0000</t>
         </is>
       </c>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="E229" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr">
+      <c r="F229" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -12058,40 +12159,40 @@
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 09:46:06 +0000</t>
         </is>
       </c>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="E230" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="F230" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Case Resolved" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -12110,39 +12211,39 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
         </is>
       </c>
-      <c r="E229" s="2" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="F231" s="2" t="inlineStr">
         <is>
           <t>A passkey is required for account access starting in two weeks</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>96
  For security, set up passkey login to maintain account access
@@ -12158,39 +12259,39 @@
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 04:58:43 +0000</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="F232" s="2" t="inlineStr">
         <is>
           <t>A returns experience customers actually like</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>96
  Faster resolutions for buyers, less friction for you.
@@ -12215,39 +12316,39 @@
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 00:17:41 +0000</t>
         </is>
       </c>
-      <c r="E231" s="2" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>View your US Q4-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q4-2026
@@ -12277,39 +12378,39 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E232" s="2" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -12338,39 +12439,39 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:44:18 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -12392,39 +12493,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 10:57:46 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -12452,40 +12553,40 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 21:52:15 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now Sell as Used and includes refurbished
  items</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>96
  Recover more value from your eligible FBA returns.
@@ -12500,39 +12601,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 10:15:39 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -12560,39 +12661,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:51:44 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfilment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready
 Position inventory, activate savings, and make your delivery speed visible. ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌
@@ -12608,39 +12709,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -12663,39 +12764,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -12723,39 +12824,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
